--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136304863</v>
       </c>
       <c r="B4" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136305330</v>
       </c>
       <c r="B5" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136305493</v>
       </c>
       <c r="B6" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>136305638</v>
       </c>
       <c r="B7" t="n">
-        <v>57927</v>
+        <v>57929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>136304930</v>
       </c>
       <c r="B25" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136304982</v>
       </c>
       <c r="B26" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>136305478</v>
       </c>
       <c r="B27" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>136305601</v>
       </c>
       <c r="B28" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136305405</v>
       </c>
       <c r="B29" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4528,6 +4528,250 @@
       <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131445502</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136983368</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56875</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>471259</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6544047</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136983368</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136983352</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56889</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Diamanten, Diamanten, Nrk</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>471259</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6544047</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skagershult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136983352</t>
         </is>
       </c>
     </row>
@@ -4565,6 +4809,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4536,7 +4536,7 @@
         <v>136983368</v>
       </c>
       <c r="B34" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136983352</v>
       </c>
       <c r="B35" t="n">
-        <v>56889</v>
+        <v>56902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4536,7 +4536,7 @@
         <v>136983368</v>
       </c>
       <c r="B34" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136983352</v>
       </c>
       <c r="B35" t="n">
-        <v>56902</v>
+        <v>56904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4562,11 +4562,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -4684,11 +4680,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>autobox</t>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4536,7 +4536,7 @@
         <v>136983368</v>
       </c>
       <c r="B34" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136983352</v>
       </c>
       <c r="B35" t="n">
-        <v>56904</v>
+        <v>56914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4536,7 +4536,7 @@
         <v>136983368</v>
       </c>
       <c r="B34" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136983352</v>
       </c>
       <c r="B35" t="n">
-        <v>56914</v>
+        <v>56915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 54304-2022 artfynd.xlsx
+++ b/artfynd/A 54304-2022 artfynd.xlsx
@@ -4536,7 +4536,7 @@
         <v>136983368</v>
       </c>
       <c r="B34" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136983352</v>
       </c>
       <c r="B35" t="n">
-        <v>56915</v>
+        <v>56918</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
